--- a/docs/AI测试用例管理平台_V1.0_排期表.xlsx
+++ b/docs/AI测试用例管理平台_V1.0_排期表.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -658,7 +658,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>用户项目权限（3/4/22）</t>
+          <t>M3｜评审深化与版本安全（7/9/10/11/14）</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -668,51 +668,51 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>项目 4 类角色与系统角色分离、项目成员管理、接口级数据隔离、版本管理、模块树、菜单对齐</t>
+          <t>字段级/步骤级驳回、驳回类型多选+修改要求、AI 修改新版本+接受/拒绝确认流、完整版本历史与恢复、乐观锁并发、回收站</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>08-31 ~ 09-11</t>
+          <t>08-31（周一）~ 09-11（周五）</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2 周</t>
+          <t>10 个工作日</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>需求管理与追溯（5/21）</t>
+          <t>M4｜测试计划与执行增强（12/13）</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>部分满足</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>需求实体化（列表/状态/附件/原文分层）、11 项结构化 AI 分析、待确认事项流转、用例→测试点追溯字段、存量迁移演练</t>
+          <t>测试计划、用例快照、任务分配与重分配留痕、执行挂到计划、执行附件（图片/视频/日志）</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>09-14 ~ 09-25</t>
+          <t>09-14（周一）~ 09-18（周五）</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2 周</t>
+          <t>5 个工作日</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>评审深化与版本安全（7/9/10/11/14）</t>
+          <t>M1｜用户项目权限（3/4/22）</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -722,51 +722,51 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>字段级/步骤级驳回、驳回类型多选+修改要求、AI 修改新版本+接受/拒绝确认流、完整版本历史与恢复、乐观锁并发、回收站</t>
+          <t>项目 4 类角色与系统角色分离、项目成员管理、接口级数据隔离、版本管理、模块树、菜单对齐</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>09-28 ~ 10-16（含国庆）</t>
+          <t>09-21（周一）~ 10-01（周四）</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>3 周</t>
+          <t>9 个工作日</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>测试计划与执行增强（12/13/14）</t>
+          <t>M2｜需求管理与追溯（5/21）</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>部分满足</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>测试计划、用例快照、任务分配与重分配留痕、执行附件（图片/视频/日志）、Excel 导入五步校验、人工新增/复制用例、批量补齐</t>
+          <t>需求实体化（列表/状态/附件/原文分层）、11 项结构化 AI 分析、待确认事项流转、用例→测试点追溯字段、存量迁移演练</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>10-19 ~ 10-30</t>
+          <t>10-02（周五）~ 10-14（周三）</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2 周</t>
+          <t>9 个工作日</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AI 中心与统计审计（15/16/17/18/20）</t>
+          <t>M5｜AI 中心与统计审计（15/16/17/18/20）</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -781,58 +781,85 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>11-02 ~ 11-13</t>
+          <t>10-15（周四）~ 10-27（周二）</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2 周</t>
+          <t>9 个工作日</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>M4b｜用例导入与批量维护（14）</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Excel 导入五步校验（上传→解析→预览→校验→确认，逐行错误提示）、人工新增/复制用例、批量补齐（优先级/标签/模块、批量加入计划、批量分配、批量删除）</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>10-28（周三）~ 10-30（周五）</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>3 个工作日</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>验收（23）</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>存量正式迁移、25 条核心规则逐条走查、缺陷缓冲</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>11-16 ~ 11-20</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>1 周</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>11-02（周一）~ 11-06（周五）</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>5 个工作日</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr"/>
-      <c r="C13" s="7" t="inlineStr"/>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>08-31 开工 → 11-20 验收完成</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>11 周</t>
+      <c r="B14" s="8" t="inlineStr"/>
+      <c r="C14" s="7" t="inlineStr"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>08-31 开工 → 11-06 验收完成（全按工作日排，不含中国节假日）</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>50 个工作日（10 周）</t>
         </is>
       </c>
     </row>
